--- a/database/event/4697/event_4697_evp_summary.xlsx
+++ b/database/event/4697/event_4697_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.3161</v>
+        <v>10.3116</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5243</v>
+        <v>5.5219</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7461</v>
+        <v>3.6642</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3161</v>
+        <v>10.3116</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0323</v>
+        <v>5.0278</v>
       </c>
       <c r="G2" t="n">
         <v>5.2838</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5876</v>
+        <v>5.5805</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6397</v>
+        <v>5.6748</v>
       </c>
       <c r="J2" t="n">
         <v>5.2838</v>
@@ -529,7 +529,7 @@
         <v>250</v>
       </c>
       <c r="M2" t="n">
-        <v>10.9235</v>
+        <v>10.9586</v>
       </c>
       <c r="N2" t="n">
         <v>474</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.860099999999999</v>
+        <v>8.840299999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>4.7446</v>
+        <v>4.734</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1579</v>
+        <v>3.0781</v>
       </c>
       <c r="E3" t="n">
-        <v>8.860099999999999</v>
+        <v>8.840299999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1366</v>
+        <v>4.1168</v>
       </c>
       <c r="G3" t="n">
         <v>4.7235</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1832</v>
+        <v>4.152</v>
       </c>
       <c r="I3" t="n">
         <v>4.2222</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1361</v>
+        <v>7.2399</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8214</v>
+        <v>3.877</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4615</v>
+        <v>2.4405</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1361</v>
+        <v>7.2399</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7173</v>
+        <v>1.8211</v>
       </c>
       <c r="G4" t="n">
         <v>5.4188</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7173</v>
+        <v>1.8211</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7333</v>
+        <v>1.8519</v>
       </c>
       <c r="J4" t="n">
         <v>5.4188</v>
@@ -621,7 +621,7 @@
         <v>250</v>
       </c>
       <c r="M4" t="n">
-        <v>7.1521</v>
+        <v>7.2707</v>
       </c>
       <c r="N4" t="n">
         <v>474</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.765</v>
+        <v>6.7451</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6227</v>
+        <v>3.612</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3115</v>
+        <v>2.2433</v>
       </c>
       <c r="E5" t="n">
-        <v>6.765</v>
+        <v>6.7451</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6678</v>
+        <v>2.6479</v>
       </c>
       <c r="G5" t="n">
         <v>4.0972</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6678</v>
+        <v>2.6479</v>
       </c>
       <c r="I5" t="n">
         <v>2.6926</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9617</v>
+        <v>5.9653</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1925</v>
+        <v>3.1944</v>
       </c>
       <c r="D6" t="n">
-        <v>1.987</v>
+        <v>1.9327</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9617</v>
+        <v>5.9653</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8663</v>
+        <v>4.8152</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0954</v>
+        <v>1.1501</v>
       </c>
       <c r="H6" t="n">
-        <v>7.0651</v>
+        <v>6.8124</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7265</v>
+        <v>5.5216</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0954</v>
+        <v>1.1501</v>
       </c>
       <c r="K6" t="n">
         <v>143</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>6.821899999999999</v>
+        <v>6.6717</v>
       </c>
       <c r="N6" t="n">
         <v>222</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8325</v>
+        <v>5.9617</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1233</v>
+        <v>3.1925</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9348</v>
+        <v>1.9312</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8325</v>
+        <v>5.9617</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6824</v>
+        <v>4.8663</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1501</v>
+        <v>1.0954</v>
       </c>
       <c r="H7" t="n">
-        <v>6.2777</v>
+        <v>7.3825</v>
       </c>
       <c r="I7" t="n">
-        <v>5.0883</v>
+        <v>5.9837</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1501</v>
+        <v>1.0954</v>
       </c>
       <c r="K7" t="n">
         <v>143</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2384</v>
+        <v>7.0791</v>
       </c>
       <c r="N7" t="n">
         <v>222</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5952</v>
+        <v>4.5776</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4607</v>
+        <v>2.4513</v>
       </c>
       <c r="D8" t="n">
-        <v>1.435</v>
+        <v>1.3798</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5952</v>
+        <v>4.5776</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3656</v>
+        <v>2.348</v>
       </c>
       <c r="G8" t="n">
         <v>2.2296</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3656</v>
+        <v>2.348</v>
       </c>
       <c r="I8" t="n">
         <v>2.3876</v>
@@ -814,262 +814,262 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1579</v>
+        <v>4.2726</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2266</v>
+        <v>2.288</v>
       </c>
       <c r="D9" t="n">
         <v>1.2583</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1579</v>
+        <v>4.2726</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1361</v>
+        <v>3.3202</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0218</v>
+        <v>0.9524</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1361</v>
+        <v>3.3202</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1361</v>
+        <v>2.6911</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0218</v>
+        <v>0.9524</v>
       </c>
       <c r="K9" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L9" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1579</v>
+        <v>3.6435</v>
       </c>
       <c r="N9" t="n">
-        <v>240</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0613</v>
+        <v>4.1901</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1748</v>
+        <v>2.2438</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2193</v>
+        <v>1.2254</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0613</v>
+        <v>4.1901</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1089</v>
+        <v>3.1683</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9524</v>
+        <v>1.0218</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1089</v>
+        <v>3.1683</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5198</v>
+        <v>3.1683</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9524</v>
+        <v>1.0218</v>
       </c>
       <c r="K10" t="n">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="L10" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4722</v>
+        <v>4.1901</v>
       </c>
       <c r="N10" t="n">
-        <v>295</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6087</v>
+        <v>3.8596</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9325</v>
+        <v>2.0668</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0365</v>
+        <v>1.0938</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6087</v>
+        <v>3.8596</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2221</v>
+        <v>3.7929</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="H11" t="n">
-        <v>4.426</v>
+        <v>3.7929</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5874</v>
+        <v>3.0743</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="K11" t="n">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="L11" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>2.974</v>
+        <v>3.141</v>
       </c>
       <c r="N11" t="n">
-        <v>222</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6069</v>
+        <v>3.6087</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9315</v>
+        <v>1.9325</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0357</v>
+        <v>0.9938</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6069</v>
+        <v>3.6087</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7851</v>
+        <v>4.2221</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8219</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7851</v>
+        <v>4.426</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7924</v>
+        <v>3.5874</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8219</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="L12" t="n">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6143</v>
+        <v>2.974</v>
       </c>
       <c r="N12" t="n">
-        <v>450</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3446</v>
+        <v>3.6011</v>
       </c>
       <c r="C13" t="n">
-        <v>1.791</v>
+        <v>1.9284</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9298</v>
+        <v>0.9908</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3446</v>
+        <v>3.6011</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2779</v>
+        <v>0.7792</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0667</v>
+        <v>2.8219</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2779</v>
+        <v>0.7792</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6568</v>
+        <v>0.7924</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0667</v>
+        <v>2.8219</v>
       </c>
       <c r="K13" t="n">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="L13" t="n">
-        <v>96</v>
+        <v>210</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7235</v>
+        <v>3.6143</v>
       </c>
       <c r="N13" t="n">
-        <v>295</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3757</v>
+        <v>2.402</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2722</v>
+        <v>1.2863</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5384</v>
+        <v>0.513</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3757</v>
+        <v>2.402</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3757</v>
+        <v>2.402</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3757</v>
+        <v>2.402</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3757</v>
+        <v>2.402</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3757</v>
+        <v>2.402</v>
       </c>
       <c r="N14" t="n">
         <v>193</v>
@@ -1090,32 +1090,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3418</v>
+        <v>2.3757</v>
       </c>
       <c r="C15" t="n">
-        <v>1.254</v>
+        <v>1.2722</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5026</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3418</v>
+        <v>2.3757</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3418</v>
+        <v>2.3757</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3418</v>
+        <v>2.3757</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3418</v>
+        <v>2.3757</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3418</v>
+        <v>2.3757</v>
       </c>
       <c r="N15" t="n">
         <v>193</v>
@@ -1146,7 +1146,7 @@
         <v>1.2438</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5169</v>
+        <v>0.4814</v>
       </c>
       <c r="E16" t="n">
         <v>2.3226</v>
@@ -1192,7 +1192,7 @@
         <v>1.2277</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5048</v>
+        <v>0.4695</v>
       </c>
       <c r="E17" t="n">
         <v>2.2926</v>
@@ -1238,7 +1238,7 @@
         <v>1.1411</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4395</v>
+        <v>0.405</v>
       </c>
       <c r="E18" t="n">
         <v>2.1309</v>
@@ -1284,7 +1284,7 @@
         <v>1.1386</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4376</v>
+        <v>0.4032</v>
       </c>
       <c r="E19" t="n">
         <v>2.1262</v>
@@ -1320,1197 +1320,1197 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9828</v>
+        <v>2.0108</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0618</v>
+        <v>1.0768</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3796</v>
+        <v>0.3572</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9828</v>
+        <v>2.0108</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9828</v>
+        <v>3.0108</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9828</v>
+        <v>3.0108</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9828</v>
+        <v>2.4403</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9828</v>
+        <v>1.4403</v>
       </c>
       <c r="N20" t="n">
-        <v>173</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9629</v>
+        <v>1.9828</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0511</v>
+        <v>1.0618</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3716</v>
+        <v>0.346</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9629</v>
+        <v>1.9828</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2132</v>
+        <v>1.9828</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2503</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2132</v>
+        <v>1.9828</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2339</v>
+        <v>1.9828</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2503</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="L21" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9836</v>
+        <v>1.9828</v>
       </c>
       <c r="N21" t="n">
-        <v>450</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8511</v>
+        <v>1.9464</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9913</v>
+        <v>1.0423</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3264</v>
+        <v>0.3315</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8511</v>
+        <v>1.9464</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2559</v>
+        <v>2.1967</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4048</v>
+        <v>-0.2503</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2559</v>
+        <v>2.1967</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8285</v>
+        <v>2.2339</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4048</v>
+        <v>-0.2503</v>
       </c>
       <c r="K22" t="n">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="L22" t="n">
-        <v>96</v>
+        <v>210</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4237</v>
+        <v>1.9836</v>
       </c>
       <c r="N22" t="n">
-        <v>295</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.751</v>
+        <v>1.8511</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9377</v>
+        <v>0.9913</v>
       </c>
       <c r="D23" t="n">
-        <v>0.286</v>
+        <v>0.2936</v>
       </c>
       <c r="E23" t="n">
-        <v>1.751</v>
+        <v>1.8511</v>
       </c>
       <c r="F23" t="n">
-        <v>2.751</v>
+        <v>2.2559</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>-0.4048</v>
       </c>
       <c r="H23" t="n">
-        <v>2.751</v>
+        <v>2.2559</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2297</v>
+        <v>1.8285</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>-0.4048</v>
       </c>
       <c r="K23" t="n">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="L23" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2297</v>
+        <v>1.4237</v>
       </c>
       <c r="N23" t="n">
-        <v>222</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7367</v>
+        <v>1.8381</v>
       </c>
       <c r="C24" t="n">
-        <v>0.93</v>
+        <v>0.9843</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2802</v>
+        <v>0.2884</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7367</v>
+        <v>1.8381</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7367</v>
+        <v>2.3175</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.4794</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7367</v>
+        <v>2.3175</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7367</v>
+        <v>2.3175</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.4794</v>
       </c>
       <c r="K24" t="n">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7367</v>
+        <v>1.8381</v>
       </c>
       <c r="N24" t="n">
-        <v>107</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7247</v>
+        <v>1.7883</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9236</v>
+        <v>0.9576</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2754</v>
+        <v>0.2685</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7247</v>
+        <v>1.7883</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7247</v>
+        <v>1.7883</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7247</v>
+        <v>1.7883</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7247</v>
+        <v>1.7883</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7247</v>
+        <v>1.7883</v>
       </c>
       <c r="N25" t="n">
-        <v>202</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6982</v>
+        <v>1.7247</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9094</v>
+        <v>0.9236</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2647</v>
+        <v>0.2432</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6982</v>
+        <v>1.7247</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2977</v>
+        <v>1.7247</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5995</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2977</v>
+        <v>1.7247</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2977</v>
+        <v>1.7247</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5995</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="L26" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6982</v>
+        <v>1.7247</v>
       </c>
       <c r="N26" t="n">
-        <v>240</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5101</v>
+        <v>1.7129</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8087</v>
+        <v>0.9173</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1887</v>
+        <v>0.2385</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5101</v>
+        <v>1.7129</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5101</v>
+        <v>1.7129</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5101</v>
+        <v>1.7129</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5101</v>
+        <v>1.7129</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.5101</v>
+        <v>1.7129</v>
       </c>
       <c r="N27" t="n">
-        <v>173</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3513</v>
+        <v>1.6982</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7236</v>
+        <v>0.9094</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1245</v>
+        <v>0.2327</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3513</v>
+        <v>1.6982</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3513</v>
+        <v>2.2977</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.5995</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3513</v>
+        <v>2.2977</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3513</v>
+        <v>2.2977</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.5995</v>
       </c>
       <c r="K28" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3513</v>
+        <v>1.6982</v>
       </c>
       <c r="N28" t="n">
-        <v>188</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2529</v>
+        <v>1.5101</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.8087</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0848</v>
+        <v>0.1577</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2529</v>
+        <v>1.5101</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8427</v>
+        <v>1.5101</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4102</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8427</v>
+        <v>1.5101</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8427</v>
+        <v>1.5101</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4102</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="L29" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2529</v>
+        <v>1.5101</v>
       </c>
       <c r="N29" t="n">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1144</v>
+        <v>1.4223</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5968</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0288</v>
+        <v>0.1227</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1144</v>
+        <v>1.4223</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1144</v>
+        <v>1.0121</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.4102</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1144</v>
+        <v>1.0121</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1144</v>
+        <v>1.0121</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.4102</v>
       </c>
       <c r="K30" t="n">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1144</v>
+        <v>1.4223</v>
       </c>
       <c r="N30" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9496</v>
+        <v>1.3513</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5085</v>
+        <v>0.7236</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0377</v>
+        <v>0.0944</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9496</v>
+        <v>1.3513</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9496</v>
+        <v>1.3513</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9496</v>
+        <v>1.3513</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9496</v>
+        <v>1.3513</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9496</v>
+        <v>1.3513</v>
       </c>
       <c r="N31" t="n">
-        <v>77</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9393</v>
+        <v>1.1335</v>
       </c>
       <c r="C32" t="n">
-        <v>0.503</v>
+        <v>0.607</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0419</v>
+        <v>0.0077</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9393</v>
+        <v>1.1335</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4187</v>
+        <v>1.9236</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4794</v>
+        <v>-0.7901</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4187</v>
+        <v>1.9236</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4187</v>
+        <v>1.9236</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4794</v>
+        <v>-0.7901</v>
       </c>
       <c r="K32" t="n">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="L32" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9393</v>
+        <v>1.1335</v>
       </c>
       <c r="N32" t="n">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Luken</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9214</v>
+        <v>1.1144</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4934</v>
+        <v>0.5968</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0491</v>
+        <v>0.0001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9214</v>
+        <v>1.1144</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9214</v>
+        <v>1.1144</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9214</v>
+        <v>1.1144</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9214</v>
+        <v>1.1144</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9214</v>
+        <v>1.1144</v>
       </c>
       <c r="N33" t="n">
-        <v>101</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8774</v>
+        <v>0.9496</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4698</v>
+        <v>0.5085</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0669</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8774</v>
+        <v>0.9496</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8774</v>
+        <v>0.9496</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8774</v>
+        <v>0.9496</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8774</v>
+        <v>0.9496</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8774</v>
+        <v>0.9496</v>
       </c>
       <c r="N34" t="n">
-        <v>202</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Luken</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8495</v>
+        <v>0.9214</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4549</v>
+        <v>0.4934</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8495</v>
+        <v>0.9214</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8495</v>
+        <v>0.9214</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8495</v>
+        <v>0.9214</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8495</v>
+        <v>0.9214</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8495</v>
+        <v>0.9214</v>
       </c>
       <c r="N35" t="n">
-        <v>173</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8002</v>
+        <v>0.8495</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4285</v>
+        <v>0.4549</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1055</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8002</v>
+        <v>0.8495</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8002</v>
+        <v>0.8495</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8002</v>
+        <v>0.8495</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8002</v>
+        <v>0.8495</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8002</v>
+        <v>0.8495</v>
       </c>
       <c r="N36" t="n">
-        <v>202</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7698</v>
+        <v>0.8002</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4122</v>
+        <v>0.4285</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1104</v>
+        <v>-0.1251</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7698</v>
+        <v>0.8002</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7698</v>
+        <v>0.8002</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7698</v>
+        <v>0.8002</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7698</v>
+        <v>0.8002</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7698</v>
+        <v>0.8002</v>
       </c>
       <c r="N37" t="n">
-        <v>107</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7377</v>
+        <v>0.7698</v>
       </c>
       <c r="C38" t="n">
-        <v>0.395</v>
+        <v>0.4122</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1233</v>
+        <v>-0.1372</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7377</v>
+        <v>0.7698</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7377</v>
+        <v>0.7698</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7377</v>
+        <v>0.7698</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7377</v>
+        <v>0.7698</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7377</v>
+        <v>0.7698</v>
       </c>
       <c r="N38" t="n">
-        <v>193</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7126</v>
+        <v>0.7377</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3816</v>
+        <v>0.395</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1335</v>
+        <v>-0.15</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7126</v>
+        <v>0.7377</v>
       </c>
       <c r="F39" t="n">
-        <v>1.5027</v>
+        <v>0.7377</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7901</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5027</v>
+        <v>0.7377</v>
       </c>
       <c r="I39" t="n">
-        <v>1.5027</v>
+        <v>0.7377</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7901</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7125999999999999</v>
+        <v>0.7377</v>
       </c>
       <c r="N39" t="n">
-        <v>240</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5511</v>
+        <v>0.7254</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2951</v>
+        <v>0.3885</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1987</v>
+        <v>-0.1549</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5511</v>
+        <v>0.7254</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3331</v>
+        <v>2.3044</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.782</v>
+        <v>-1.579</v>
       </c>
       <c r="H40" t="n">
-        <v>1.3331</v>
+        <v>2.3044</v>
       </c>
       <c r="I40" t="n">
-        <v>1.3331</v>
+        <v>2.3434</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.782</v>
+        <v>-1.579</v>
       </c>
       <c r="K40" t="n">
-        <v>145</v>
+        <v>224</v>
       </c>
       <c r="L40" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5510999999999999</v>
+        <v>0.7644</v>
       </c>
       <c r="N40" t="n">
-        <v>219</v>
+        <v>474</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>motm</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>0.282</v>
+        <v>0.3706</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2086</v>
+        <v>-0.1682</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5266999999999999</v>
+        <v>1.474</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.782</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5266999999999999</v>
+        <v>1.474</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5266999999999999</v>
+        <v>1.474</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.782</v>
       </c>
       <c r="K41" t="n">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>188</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>motm</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4891</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2619</v>
+        <v>0.282</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2238</v>
+        <v>-0.2341</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4891</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4891</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4891</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4891</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4891</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>107</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4787</v>
+        <v>0.4891</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2563</v>
+        <v>0.2619</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.228</v>
+        <v>-0.2491</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4787</v>
+        <v>0.4891</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4787</v>
+        <v>0.4891</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4787</v>
+        <v>0.4891</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4787</v>
+        <v>0.4891</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4787</v>
+        <v>0.4891</v>
       </c>
       <c r="N43" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.462</v>
+        <v>0.4787</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2474</v>
+        <v>0.2563</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2347</v>
+        <v>-0.2532</v>
       </c>
       <c r="E44" t="n">
-        <v>0.462</v>
+        <v>0.4787</v>
       </c>
       <c r="F44" t="n">
-        <v>1.462</v>
+        <v>0.4787</v>
       </c>
       <c r="G44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.462</v>
+        <v>0.4787</v>
       </c>
       <c r="I44" t="n">
-        <v>1.462</v>
+        <v>0.4787</v>
       </c>
       <c r="J44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="L44" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.462</v>
+        <v>0.4787</v>
       </c>
       <c r="N44" t="n">
-        <v>219</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4201</v>
+        <v>0.4633</v>
       </c>
       <c r="C45" t="n">
-        <v>0.225</v>
+        <v>0.2481</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2517</v>
+        <v>-0.2593</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4201</v>
+        <v>0.4633</v>
       </c>
       <c r="F45" t="n">
-        <v>1.9991</v>
+        <v>1.4633</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.579</v>
+        <v>-1</v>
       </c>
       <c r="H45" t="n">
-        <v>1.9991</v>
+        <v>1.4633</v>
       </c>
       <c r="I45" t="n">
-        <v>2.0178</v>
+        <v>1.4633</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.579</v>
+        <v>-1</v>
       </c>
       <c r="K45" t="n">
-        <v>224</v>
+        <v>145</v>
       </c>
       <c r="L45" t="n">
-        <v>250</v>
+        <v>74</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4387999999999999</v>
+        <v>0.4633</v>
       </c>
       <c r="N45" t="n">
-        <v>474</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46">
@@ -2526,7 +2526,7 @@
         <v>0.211</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2622</v>
+        <v>-0.2869</v>
       </c>
       <c r="E46" t="n">
         <v>0.3941</v>
@@ -2572,7 +2572,7 @@
         <v>0.139</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3165</v>
+        <v>-0.3405</v>
       </c>
       <c r="E47" t="n">
         <v>0.2595</v>
@@ -2618,7 +2618,7 @@
         <v>0.1367</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3183</v>
+        <v>-0.3422</v>
       </c>
       <c r="E48" t="n">
         <v>0.2552</v>
@@ -2664,7 +2664,7 @@
         <v>0.1256</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3266</v>
+        <v>-0.3504</v>
       </c>
       <c r="E49" t="n">
         <v>0.2346</v>
@@ -2710,7 +2710,7 @@
         <v>0.1062</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3413</v>
+        <v>-0.3649</v>
       </c>
       <c r="E50" t="n">
         <v>0.1983</v>
@@ -2756,7 +2756,7 @@
         <v>0.0241</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4032</v>
+        <v>-0.426</v>
       </c>
       <c r="E51" t="n">
         <v>0.045</v>
@@ -2802,7 +2802,7 @@
         <v>0.0216</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.405</v>
+        <v>-0.4278</v>
       </c>
       <c r="E52" t="n">
         <v>0.0404</v>
@@ -2838,93 +2838,93 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0703</v>
+        <v>0.0133</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0376</v>
+        <v>0.0071</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4498</v>
+        <v>-0.4386</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0703</v>
+        <v>0.0133</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0703</v>
+        <v>1.0133</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0703</v>
+        <v>1.0133</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0703</v>
+        <v>1.0133</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K53" t="n">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0703</v>
+        <v>0.01330000000000009</v>
       </c>
       <c r="N53" t="n">
-        <v>193</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0993</v>
+        <v>0.0054</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0532</v>
+        <v>0.0029</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4615</v>
+        <v>-0.4418</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0993</v>
+        <v>0.0054</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="G54" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="J54" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="L54" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.09930000000000005</v>
+        <v>0.0054</v>
       </c>
       <c r="N54" t="n">
-        <v>219</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55">
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1364</v>
+        <v>-0.1231</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.073</v>
+        <v>-0.0659</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4765</v>
+        <v>-0.493</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1364</v>
+        <v>-0.1231</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.786</v>
+        <v>-1.7727</v>
       </c>
       <c r="G55" t="n">
         <v>1.6496</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.786</v>
+        <v>-1.7727</v>
       </c>
       <c r="I55" t="n">
         <v>-1.8027</v>
@@ -2986,7 +2986,7 @@
         <v>-0.128</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.518</v>
+        <v>-0.5392</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2391</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1598</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5419</v>
+        <v>-0.5628</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2984</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1792</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5565</v>
+        <v>-0.5772</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3346</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2005</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5726</v>
+        <v>-0.5931</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3744</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4112</v>
+        <v>-0.4111</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2202</v>
+        <v>-0.2201</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5875</v>
+        <v>-0.6077</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4112</v>
+        <v>-0.4111</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.824</v>
       </c>
       <c r="G60" t="n">
         <v>0.4129</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.824</v>
       </c>
       <c r="I60" t="n">
         <v>-0.6679</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2238</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.418</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2336</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5976</v>
+        <v>-0.6177</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4362</v>
@@ -3298,323 +3298,323 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6081</v>
+        <v>-0.5142</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3256</v>
+        <v>-0.2754</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.667</v>
+        <v>-0.6488</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6081</v>
+        <v>-0.5142</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6081</v>
+        <v>-0.5142</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6081</v>
+        <v>-0.5142</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6081</v>
+        <v>-0.5142</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6081</v>
+        <v>-0.5142</v>
       </c>
       <c r="N63" t="n">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6484</v>
+        <v>-0.6081</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3472</v>
+        <v>-0.3256</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6833</v>
+        <v>-0.6862</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6484</v>
+        <v>-0.6081</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6484</v>
+        <v>-0.6081</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6484</v>
+        <v>-0.6081</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6484</v>
+        <v>-0.6081</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6484</v>
+        <v>-0.6081</v>
       </c>
       <c r="N64" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6902</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3696</v>
+        <v>-0.336</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7002</v>
+        <v>-0.6939</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6902</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1827</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.5075</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1827</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1844</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.5075</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="L65" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6919</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>450</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6983</v>
+        <v>-0.6888</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3739</v>
+        <v>-0.3689</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7035</v>
+        <v>-0.7183</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6983</v>
+        <v>-0.6888</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6983</v>
+        <v>-0.1813</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-0.5075</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6983</v>
+        <v>-0.1813</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6983</v>
+        <v>-0.1844</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-0.5075</v>
       </c>
       <c r="K66" t="n">
-        <v>101</v>
+        <v>240</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6983</v>
+        <v>-0.6919</v>
       </c>
       <c r="N66" t="n">
-        <v>101</v>
+        <v>450</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7278</v>
+        <v>-0.6983</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3897</v>
+        <v>-0.3739</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7154</v>
+        <v>-0.7221</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7278</v>
+        <v>-0.6983</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7278</v>
+        <v>-0.6983</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7278</v>
+        <v>-0.6983</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7278</v>
+        <v>-0.6983</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7278</v>
+        <v>-0.6983</v>
       </c>
       <c r="N67" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7715</v>
+        <v>-0.7278</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4131</v>
+        <v>-0.3897</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.733</v>
+        <v>-0.7339</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7715</v>
+        <v>-0.7278</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7715</v>
+        <v>-0.7278</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7715</v>
+        <v>-0.7278</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7715</v>
+        <v>-0.7278</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>188</v>
+        <v>89</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7715</v>
+        <v>-0.7278</v>
       </c>
       <c r="N68" t="n">
-        <v>188</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7766</v>
+        <v>-0.7715</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4159</v>
+        <v>-0.4131</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7351</v>
+        <v>-0.7513</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7766</v>
+        <v>-0.7715</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7766</v>
+        <v>-0.7715</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7766</v>
+        <v>-0.7715</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7766</v>
+        <v>-0.7715</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7766</v>
+        <v>-0.7715</v>
       </c>
       <c r="N69" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70">
@@ -3630,7 +3630,7 @@
         <v>-0.4566</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7658</v>
+        <v>-0.7836</v>
       </c>
       <c r="E70" t="n">
         <v>-0.8526</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4806</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.7839</v>
+        <v>-0.8014</v>
       </c>
       <c r="E71" t="n">
         <v>-0.8974</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5929</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8686</v>
+        <v>-0.885</v>
       </c>
       <c r="E72" t="n">
         <v>-1.1072</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6768999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9475</v>
       </c>
       <c r="E73" t="n">
         <v>-1.264</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7506</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9876</v>
+        <v>-1.0023</v>
       </c>
       <c r="E74" t="n">
         <v>-1.4017</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7712</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0032</v>
+        <v>-1.0177</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4402</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.6541</v>
+        <v>-1.5643</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.8858</v>
+        <v>-0.8377</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0896</v>
+        <v>-1.0671</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.6541</v>
+        <v>-1.5643</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.6541</v>
+        <v>-1.5643</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.6541</v>
+        <v>-1.5643</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.6541</v>
+        <v>-1.5643</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.6541</v>
+        <v>-1.5643</v>
       </c>
       <c r="N76" t="n">
         <v>202</v>
@@ -3952,7 +3952,7 @@
         <v>-0.923</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1177</v>
+        <v>-1.1306</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7237</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9467</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1356</v>
+        <v>-1.1482</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7679</v>
@@ -4044,7 +4044,7 @@
         <v>-0.9668</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1507</v>
+        <v>-1.1632</v>
       </c>
       <c r="E79" t="n">
         <v>-1.8054</v>
@@ -4090,7 +4090,7 @@
         <v>-1.3237</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.42</v>
+        <v>-1.4287</v>
       </c>
       <c r="E80" t="n">
         <v>-2.4719</v>
@@ -4136,7 +4136,7 @@
         <v>-1.8105</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7872</v>
+        <v>-1.7909</v>
       </c>
       <c r="E81" t="n">
         <v>-3.3809</v>
